--- a/event_feedback_forms/008_event_debrief_form--event_feedback_forms.xlsx
+++ b/event_feedback_forms/008_event_debrief_form--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Conference'}</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'seminar'}</t>
+          <t>seminar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Seminar'}</t>
+          <t>Seminar</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'panel'}</t>
+          <t>panel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Panel'}</t>
+          <t>Panel</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Training'}</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'not_satisfied_at_all'}</t>
+          <t>not_satisfied_at_all</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Not Satisfied At All'}</t>
+          <t>Not Satisfied At All</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Good'}</t>
+          <t>Somewhat Good</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_good'}</t>
+          <t>not_good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Good'}</t>
+          <t>Not Good</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
